--- a/图云ITSS/资料整理/人员花名册.xlsx
+++ b/图云ITSS/资料整理/人员花名册.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="18180" firstSheet="1" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="18180" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="2021高新认定清单" sheetId="4" r:id="rId1"/>
     <sheet name="人员花名册" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -87,6 +88,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>请提供最新版本
@@ -97,6 +99,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>新营业执照</t>
@@ -106,6 +109,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>、</t>
@@ -115,6 +119,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>旧营业执照</t>
@@ -124,6 +129,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>、</t>
@@ -133,6 +139,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>企业名称变更核准通知书（线上办理的，提供电子版即可）</t>
@@ -150,6 +157,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>专项审计报告</t>
@@ -159,6 +167,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>（近三年的高新技术企业专项审计情况一览表，研发费用归集情况一览表）</t>
@@ -173,6 +182,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>2018年、2019年的</t>
@@ -182,6 +192,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>年审审计报告</t>
@@ -196,6 +207,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>2018年、2019年的年度汇算清缴（</t>
@@ -205,6 +217,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>所得税年度</t>
@@ -214,6 +227,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>纳税申报表，封皮页+主表+附表+财务报表）</t>
@@ -228,6 +242,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -237,6 +252,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>、所得税，非增值税</t>
@@ -246,6 +262,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
@@ -256,6 +273,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>、年度，非季度</t>
@@ -270,6 +288,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>自主研发知识产权
@@ -280,6 +299,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>授权证书首页</t>
@@ -289,6 +309,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>、</t>
@@ -298,6 +319,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>摘要页</t>
@@ -307,6 +329,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>、</t>
@@ -316,6 +339,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>年费缴费收据或</t>
@@ -325,6 +349,7 @@
         <sz val="12"/>
         <color rgb="FF0070C0"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>授权通知书和年费缴费收据</t>
@@ -333,6 +358,7 @@
       <rPr>
         <sz val="12"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
@@ -347,6 +373,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>如专利权人和公司名称不一致的，专利提供证书首页外，还需提供</t>
@@ -356,6 +383,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>登记簿副本</t>
@@ -370,6 +398,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>受让、受赠、并购</t>
@@ -379,6 +408,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>获得的专利提供</t>
@@ -388,6 +418,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>变更证明</t>
@@ -397,6 +428,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>、</t>
@@ -406,6 +438,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>授权证书首页、摘要页、年费缴费收据</t>
@@ -426,6 +459,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>销售合同</t>
@@ -435,6 +469,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>、</t>
@@ -444,6 +479,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>技术服务合同</t>
@@ -453,6 +489,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>及</t>
@@ -462,6 +499,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>对应的发票</t>
@@ -471,6 +509,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>（2018年、2019年、2020年年</t>
@@ -480,6 +519,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>每年</t>
@@ -489,6 +529,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>至少</t>
@@ -498,6 +539,7 @@
         <sz val="12"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>5份，签订时间最好是在6月份之后的</t>
@@ -507,6 +549,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>）</t>
@@ -522,6 +565,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>1.</t>
@@ -531,6 +575,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>产品应用类：产品销售合同及对应的发票；产品照片、用户使用报告、客户满意度调查等；</t>
@@ -540,6 +585,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
@@ -550,6 +596,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>检验检测类：产品检测报告、查新报告、成果登记证书、产品认定类证书等；</t>
@@ -559,6 +606,7 @@
         <sz val="12"/>
         <color theme="1"/>
         <rFont val="Tahoma"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
@@ -700,6 +748,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>是否</t>
@@ -709,6 +758,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
@@ -719,6 +769,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>是科技人员</t>
@@ -730,6 +781,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>在职/</t>
@@ -739,6 +791,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="仿宋_GB2312"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>兼职</t>
@@ -748,6 +801,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>/</t>
@@ -757,6 +811,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="仿宋_GB2312"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>临时聘用</t>
@@ -869,18 +924,25 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -888,6 +950,7 @@
       <sz val="20"/>
       <color theme="1"/>
       <name val="Tahoma"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -895,6 +958,7 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -902,42 +966,42 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Tahoma"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="仿宋_GB2312"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Tahoma"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -945,12 +1009,14 @@
       <sz val="18"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -958,13 +1024,15 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -972,24 +1040,28 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -997,22 +1069,16 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1020,6 +1086,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1028,7 +1095,8 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1036,6 +1104,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1044,6 +1113,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1052,6 +1122,7 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1059,7 +1130,8 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1067,7 +1139,8 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1075,7 +1148,8 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1083,14 +1157,16 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1098,69 +1174,242 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF0070C0"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
   <fills count="37">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1183,192 +1432,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1379,58 +1442,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1446,7 +1457,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1455,16 +1465,14 @@
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1479,7 +1487,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1494,7 +1501,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -1509,7 +1515,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1518,7 +1523,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1529,154 +1533,233 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+  <cellStyleXfs count="78">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="4" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="4" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="6" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="52">
@@ -1684,38 +1767,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1736,88 +1819,88 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="35" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="34" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="34" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="34" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="35" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="35" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="9" xfId="35" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1829,62 +1912,145 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="64">
+    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Percent" xfId="15"/>
+    <cellStyle name="Currency" xfId="16"/>
+    <cellStyle name="Currency [0]" xfId="17"/>
+    <cellStyle name="Comma" xfId="18"/>
+    <cellStyle name="Comma [0]" xfId="19"/>
+    <cellStyle name="Percent" xfId="20"/>
+    <cellStyle name="Currency" xfId="21"/>
+    <cellStyle name="Currency [0]" xfId="22"/>
+    <cellStyle name="Comma" xfId="23"/>
+    <cellStyle name="Comma [0]" xfId="24"/>
+    <cellStyle name="Percent" xfId="25"/>
+    <cellStyle name="Currency" xfId="26"/>
+    <cellStyle name="Currency [0]" xfId="27"/>
+    <cellStyle name="Comma" xfId="28"/>
+    <cellStyle name="Comma [0]" xfId="29"/>
+    <cellStyle name="千位分隔" xfId="30"/>
+    <cellStyle name="货币" xfId="31"/>
+    <cellStyle name="百分比" xfId="32"/>
+    <cellStyle name="千位分隔[0]" xfId="33"/>
+    <cellStyle name="货币[0]" xfId="34"/>
+    <cellStyle name="超链接" xfId="35"/>
+    <cellStyle name="已访问的超链接" xfId="36"/>
+    <cellStyle name="注释" xfId="37"/>
+    <cellStyle name="警告文本" xfId="38"/>
+    <cellStyle name="标题" xfId="39"/>
+    <cellStyle name="解释性文本" xfId="40"/>
+    <cellStyle name="标题 1" xfId="41"/>
+    <cellStyle name="标题 2" xfId="42"/>
+    <cellStyle name="标题 3" xfId="43"/>
+    <cellStyle name="标题 4" xfId="44"/>
+    <cellStyle name="输入" xfId="45"/>
+    <cellStyle name="输出" xfId="46"/>
+    <cellStyle name="计算" xfId="47"/>
+    <cellStyle name="检查单元格" xfId="48"/>
+    <cellStyle name="链接单元格" xfId="49"/>
+    <cellStyle name="汇总" xfId="50"/>
+    <cellStyle name="好" xfId="51"/>
+    <cellStyle name="差" xfId="52"/>
+    <cellStyle name="适中" xfId="53"/>
+    <cellStyle name="强调文字颜色 1" xfId="54"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="55"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="56"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="57"/>
+    <cellStyle name="强调文字颜色 2" xfId="58"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="59"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="60"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="61"/>
+    <cellStyle name="强调文字颜色 3" xfId="62"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="63"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="64"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="65"/>
+    <cellStyle name="强调文字颜色 4" xfId="66"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="67"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="68"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="69"/>
+    <cellStyle name="强调文字颜色 5" xfId="70"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="71"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="72"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="73"/>
+    <cellStyle name="强调文字颜色 6" xfId="74"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="75"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="76"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="77"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2177,7 +2343,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:K45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -2192,7 +2357,7 @@
     <col min="16383" max="16384" width="9" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.9" customHeight="1" spans="1:11">
+    <row r="1" spans="1:10" ht="31.9" customHeight="1">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -2202,9 +2367,10 @@
       <c r="E1" s="16"/>
       <c r="F1" s="16"/>
       <c r="G1" s="16"/>
+      <c r="H1" s="14"/>
       <c r="J1" s="17"/>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:11">
+    <row r="2" spans="1:10" ht="24" customHeight="1">
       <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
@@ -2216,9 +2382,10 @@
       <c r="E2" s="18"/>
       <c r="F2" s="18"/>
       <c r="G2" s="18"/>
+      <c r="H2" s="14"/>
       <c r="J2" s="17"/>
     </row>
-    <row r="3" ht="27" customHeight="1" spans="1:11">
+    <row r="3" spans="1:8" ht="27" customHeight="1">
       <c r="A3" s="20" t="s">
         <v>3</v>
       </c>
@@ -2240,8 +2407,9 @@
       <c r="G3" s="21" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" ht="33.95" customHeight="1" spans="1:11">
+      <c r="H3" s="14"/>
+    </row>
+    <row r="4" spans="1:8" ht="33.95" customHeight="1">
       <c r="A4" s="22" t="s">
         <v>10</v>
       </c>
@@ -2257,8 +2425,9 @@
       </c>
       <c r="F4" s="27"/>
       <c r="G4" s="21"/>
-    </row>
-    <row r="5" ht="81" customHeight="1" spans="1:11">
+      <c r="H4" s="14"/>
+    </row>
+    <row r="5" spans="1:8" ht="81" customHeight="1">
       <c r="A5" s="22" t="s">
         <v>14</v>
       </c>
@@ -2274,8 +2443,9 @@
       </c>
       <c r="F5" s="27"/>
       <c r="G5" s="21"/>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:11">
+      <c r="H5" s="14"/>
+    </row>
+    <row r="6" spans="1:8" ht="24" customHeight="1">
       <c r="A6" s="30"/>
       <c r="B6" s="23"/>
       <c r="C6" s="14" t="s">
@@ -2285,8 +2455,9 @@
       <c r="E6" s="29"/>
       <c r="F6" s="27"/>
       <c r="G6" s="21"/>
-    </row>
-    <row r="7" ht="39.95" customHeight="1" spans="1:11">
+      <c r="H6" s="14"/>
+    </row>
+    <row r="7" spans="1:8" ht="39.95" customHeight="1">
       <c r="A7" s="20" t="s">
         <v>19</v>
       </c>
@@ -2300,8 +2471,9 @@
       <c r="E7" s="34"/>
       <c r="F7" s="35"/>
       <c r="G7" s="34"/>
-    </row>
-    <row r="8" ht="38.1" customHeight="1" spans="1:11">
+      <c r="H7" s="14"/>
+    </row>
+    <row r="8" spans="1:8" ht="38.1" customHeight="1">
       <c r="A8" s="20"/>
       <c r="B8" s="36"/>
       <c r="C8" s="29" t="s">
@@ -2315,8 +2487,9 @@
       </c>
       <c r="F8" s="27"/>
       <c r="G8" s="21"/>
-    </row>
-    <row r="9" ht="42.95" customHeight="1" spans="1:11">
+      <c r="H8" s="14"/>
+    </row>
+    <row r="9" spans="1:8" ht="42.95" customHeight="1">
       <c r="A9" s="20"/>
       <c r="B9" s="36"/>
       <c r="C9" s="29" t="s">
@@ -2330,8 +2503,9 @@
       </c>
       <c r="F9" s="27"/>
       <c r="G9" s="21"/>
-    </row>
-    <row r="10" ht="90" customHeight="1" spans="1:11">
+      <c r="H9" s="14"/>
+    </row>
+    <row r="10" spans="1:8" ht="90" customHeight="1">
       <c r="A10" s="30" t="s">
         <v>27</v>
       </c>
@@ -2349,8 +2523,9 @@
       <c r="G10" s="22" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" ht="39" customHeight="1" spans="1:11">
+      <c r="H10" s="14"/>
+    </row>
+    <row r="11" spans="1:8" ht="39" customHeight="1">
       <c r="A11" s="30"/>
       <c r="B11" s="39"/>
       <c r="C11" s="40" t="s">
@@ -2362,8 +2537,9 @@
       <c r="E11" s="21"/>
       <c r="F11" s="27"/>
       <c r="G11" s="41"/>
-    </row>
-    <row r="12" ht="33.95" customHeight="1" spans="1:11">
+      <c r="H11" s="14"/>
+    </row>
+    <row r="12" spans="1:8" ht="33.95" customHeight="1">
       <c r="A12" s="41"/>
       <c r="B12" s="39"/>
       <c r="C12" s="28" t="s">
@@ -2377,8 +2553,9 @@
       </c>
       <c r="F12" s="27"/>
       <c r="G12" s="21"/>
-    </row>
-    <row r="13" ht="104.1" customHeight="1" spans="1:11">
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" spans="1:11" ht="104.1" customHeight="1">
       <c r="A13" s="20" t="s">
         <v>35</v>
       </c>
@@ -2401,7 +2578,7 @@
       <c r="J13" s="42"/>
       <c r="K13" s="42"/>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="1:11">
+    <row r="14" spans="1:11" ht="24" customHeight="1">
       <c r="A14" s="20"/>
       <c r="B14" s="39"/>
       <c r="C14" s="28" t="s">
@@ -2418,7 +2595,7 @@
       <c r="J14" s="42"/>
       <c r="K14" s="42"/>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:11">
+    <row r="15" spans="1:11" ht="24" customHeight="1">
       <c r="A15" s="20"/>
       <c r="B15" s="39"/>
       <c r="C15" s="28" t="s">
@@ -2435,7 +2612,7 @@
       <c r="J15" s="42"/>
       <c r="K15" s="42"/>
     </row>
-    <row r="16" ht="24" customHeight="1" spans="1:11">
+    <row r="16" spans="1:11" ht="24" customHeight="1">
       <c r="A16" s="20"/>
       <c r="B16" s="39"/>
       <c r="C16" s="28" t="s">
@@ -2452,7 +2629,7 @@
       <c r="J16" s="42"/>
       <c r="K16" s="42"/>
     </row>
-    <row r="17" ht="24" customHeight="1" spans="1:11">
+    <row r="17" spans="1:11" ht="24" customHeight="1">
       <c r="A17" s="20"/>
       <c r="B17" s="39"/>
       <c r="C17" s="28" t="s">
@@ -2469,7 +2646,7 @@
       <c r="J17" s="42"/>
       <c r="K17" s="42"/>
     </row>
-    <row r="18" ht="24" customHeight="1" spans="1:11">
+    <row r="18" spans="1:11" ht="24" customHeight="1">
       <c r="A18" s="20"/>
       <c r="B18" s="39"/>
       <c r="C18" s="28" t="s">
@@ -2486,7 +2663,7 @@
       <c r="J18" s="42"/>
       <c r="K18" s="42"/>
     </row>
-    <row r="19" ht="24" customHeight="1" spans="1:11">
+    <row r="19" spans="1:11" ht="24" customHeight="1">
       <c r="A19" s="20"/>
       <c r="B19" s="39"/>
       <c r="C19" s="28" t="s">
@@ -2503,7 +2680,7 @@
       <c r="J19" s="42"/>
       <c r="K19" s="42"/>
     </row>
-    <row r="20" ht="24" customHeight="1" spans="1:11">
+    <row r="20" spans="1:8" ht="24" customHeight="1">
       <c r="A20" s="22" t="s">
         <v>45</v>
       </c>
@@ -2517,8 +2694,9 @@
       <c r="E20" s="21"/>
       <c r="F20" s="27"/>
       <c r="G20" s="21"/>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:11">
+      <c r="H20" s="14"/>
+    </row>
+    <row r="21" spans="1:8" ht="24" customHeight="1">
       <c r="A21" s="30"/>
       <c r="B21" s="43"/>
       <c r="C21" s="44" t="s">
@@ -2530,8 +2708,9 @@
       <c r="E21" s="21"/>
       <c r="F21" s="27"/>
       <c r="G21" s="21"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:11">
+      <c r="H21" s="14"/>
+    </row>
+    <row r="22" spans="1:8" ht="24" customHeight="1">
       <c r="A22" s="30"/>
       <c r="B22" s="43"/>
       <c r="C22" s="44" t="s">
@@ -2543,8 +2722,9 @@
       <c r="E22" s="21"/>
       <c r="F22" s="27"/>
       <c r="G22" s="21"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:11">
+      <c r="H22" s="14"/>
+    </row>
+    <row r="23" spans="1:8" ht="24" customHeight="1">
       <c r="A23" s="30"/>
       <c r="B23" s="43"/>
       <c r="C23" s="44" t="s">
@@ -2556,8 +2736,9 @@
       <c r="E23" s="21"/>
       <c r="F23" s="27"/>
       <c r="G23" s="21"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:11">
+      <c r="H23" s="14"/>
+    </row>
+    <row r="24" spans="1:8" ht="24" customHeight="1">
       <c r="A24" s="30"/>
       <c r="B24" s="43"/>
       <c r="C24" s="44" t="s">
@@ -2569,8 +2750,9 @@
       <c r="E24" s="21"/>
       <c r="F24" s="27"/>
       <c r="G24" s="21"/>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:11">
+      <c r="H24" s="14"/>
+    </row>
+    <row r="25" spans="1:8" ht="24" customHeight="1">
       <c r="A25" s="30"/>
       <c r="B25" s="43"/>
       <c r="C25" s="44" t="s">
@@ -2582,8 +2764,9 @@
       <c r="E25" s="21"/>
       <c r="F25" s="27"/>
       <c r="G25" s="21"/>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:11">
+      <c r="H25" s="14"/>
+    </row>
+    <row r="26" spans="1:8" ht="24" customHeight="1">
       <c r="A26" s="30"/>
       <c r="B26" s="43"/>
       <c r="C26" s="44" t="s">
@@ -2595,8 +2778,9 @@
       <c r="E26" s="21"/>
       <c r="F26" s="27"/>
       <c r="G26" s="21"/>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:11">
+      <c r="H26" s="14"/>
+    </row>
+    <row r="27" spans="1:8" ht="24" customHeight="1">
       <c r="A27" s="30"/>
       <c r="B27" s="43"/>
       <c r="C27" s="44" t="s">
@@ -2608,8 +2792,9 @@
       <c r="E27" s="21"/>
       <c r="F27" s="27"/>
       <c r="G27" s="21"/>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:11">
+      <c r="H27" s="14"/>
+    </row>
+    <row r="28" spans="1:8" ht="24" customHeight="1">
       <c r="A28" s="30"/>
       <c r="B28" s="23"/>
       <c r="C28" s="28" t="s">
@@ -2621,8 +2806,9 @@
       <c r="E28" s="21"/>
       <c r="F28" s="27"/>
       <c r="G28" s="21"/>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="1:11">
+      <c r="H28" s="14"/>
+    </row>
+    <row r="29" spans="1:8" ht="24" customHeight="1">
       <c r="A29" s="30"/>
       <c r="B29" s="23"/>
       <c r="C29" s="28" t="s">
@@ -2634,8 +2820,9 @@
       <c r="E29" s="21"/>
       <c r="F29" s="27"/>
       <c r="G29" s="21"/>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="1:11">
+      <c r="H29" s="14"/>
+    </row>
+    <row r="30" spans="1:8" ht="24" customHeight="1">
       <c r="A30" s="30"/>
       <c r="B30" s="23"/>
       <c r="C30" s="45" t="s">
@@ -2649,8 +2836,9 @@
       </c>
       <c r="F30" s="27"/>
       <c r="G30" s="21"/>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="1:11">
+      <c r="H30" s="14"/>
+    </row>
+    <row r="31" spans="1:8" ht="24" customHeight="1">
       <c r="A31" s="30" t="s">
         <v>58</v>
       </c>
@@ -2666,8 +2854,9 @@
       </c>
       <c r="F31" s="27"/>
       <c r="G31" s="21"/>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:11">
+      <c r="H31" s="14"/>
+    </row>
+    <row r="32" spans="1:8" ht="24" customHeight="1">
       <c r="A32" s="30"/>
       <c r="B32" s="43"/>
       <c r="C32" s="46" t="s">
@@ -2681,8 +2870,9 @@
       </c>
       <c r="F32" s="27"/>
       <c r="G32" s="21"/>
-    </row>
-    <row r="33" ht="24" customHeight="1" spans="1:7">
+      <c r="H32" s="14"/>
+    </row>
+    <row r="33" spans="1:8" ht="24" customHeight="1">
       <c r="A33" s="30"/>
       <c r="B33" s="23"/>
       <c r="C33" s="28" t="s">
@@ -2694,8 +2884,9 @@
       <c r="E33" s="26"/>
       <c r="F33" s="27"/>
       <c r="G33" s="21"/>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="1:7">
+      <c r="H33" s="14"/>
+    </row>
+    <row r="34" spans="1:8" ht="24" customHeight="1">
       <c r="A34" s="30"/>
       <c r="B34" s="39"/>
       <c r="C34" s="28" t="s">
@@ -2709,8 +2900,9 @@
       <c r="G34" s="21" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="35" ht="24" customHeight="1" spans="1:7">
+      <c r="H34" s="14"/>
+    </row>
+    <row r="35" spans="1:8" ht="24" customHeight="1">
       <c r="A35" s="41"/>
       <c r="B35" s="43"/>
       <c r="C35" s="44" t="s">
@@ -2722,8 +2914,9 @@
       <c r="E35" s="21"/>
       <c r="F35" s="27"/>
       <c r="G35" s="21"/>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="1:7">
+      <c r="H35" s="14"/>
+    </row>
+    <row r="36" spans="1:8" ht="24" customHeight="1">
       <c r="A36" s="22" t="s">
         <v>65</v>
       </c>
@@ -2737,8 +2930,9 @@
       <c r="E36" s="21"/>
       <c r="F36" s="27"/>
       <c r="G36" s="21"/>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="1:7">
+      <c r="H36" s="14"/>
+    </row>
+    <row r="37" spans="1:8" ht="24" customHeight="1">
       <c r="A37" s="30"/>
       <c r="B37" s="43"/>
       <c r="C37" s="44" t="s">
@@ -2750,8 +2944,9 @@
       <c r="E37" s="21"/>
       <c r="F37" s="27"/>
       <c r="G37" s="21"/>
-    </row>
-    <row r="38" ht="24" customHeight="1" spans="1:7">
+      <c r="H37" s="14"/>
+    </row>
+    <row r="38" spans="1:8" ht="24" customHeight="1">
       <c r="A38" s="30"/>
       <c r="B38" s="47"/>
       <c r="C38" s="28" t="s">
@@ -2763,8 +2958,9 @@
       <c r="E38" s="21"/>
       <c r="F38" s="27"/>
       <c r="G38" s="21"/>
-    </row>
-    <row r="39" ht="24" customHeight="1" spans="1:7">
+      <c r="H38" s="14"/>
+    </row>
+    <row r="39" spans="1:8" ht="24" customHeight="1">
       <c r="A39" s="30"/>
       <c r="B39" s="43"/>
       <c r="C39" s="44" t="s">
@@ -2776,8 +2972,9 @@
       <c r="E39" s="21"/>
       <c r="F39" s="27"/>
       <c r="G39" s="21"/>
-    </row>
-    <row r="40" ht="24" customHeight="1" spans="1:7">
+      <c r="H39" s="14"/>
+    </row>
+    <row r="40" spans="1:8" ht="24" customHeight="1">
       <c r="A40" s="30"/>
       <c r="B40" s="43"/>
       <c r="C40" s="44" t="s">
@@ -2789,8 +2986,9 @@
       <c r="E40" s="21"/>
       <c r="F40" s="27"/>
       <c r="G40" s="21"/>
-    </row>
-    <row r="41" ht="24" customHeight="1" spans="1:7">
+      <c r="H40" s="14"/>
+    </row>
+    <row r="41" spans="1:8" ht="24" customHeight="1">
       <c r="A41" s="41"/>
       <c r="B41" s="47"/>
       <c r="C41" s="28" t="s">
@@ -2802,15 +3000,19 @@
       <c r="E41" s="21"/>
       <c r="F41" s="27"/>
       <c r="G41" s="21"/>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="H41" s="14"/>
+    </row>
+    <row r="42" spans="1:8" ht="15">
       <c r="A42" s="48"/>
       <c r="B42" s="49"/>
       <c r="C42" s="48"/>
       <c r="D42" s="49"/>
       <c r="E42" s="48"/>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="F42" s="15"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+    </row>
+    <row r="43" spans="1:8" ht="15">
       <c r="A43" s="50" t="s">
         <v>72</v>
       </c>
@@ -2818,18 +3020,35 @@
       <c r="C43" s="50" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+    </row>
+    <row r="44" spans="1:8" ht="15">
+      <c r="A44" s="14"/>
       <c r="B44" s="23"/>
       <c r="C44" s="50" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+    </row>
+    <row r="45" spans="1:8" ht="15">
+      <c r="A45" s="14"/>
       <c r="B45" s="47"/>
       <c r="C45" s="50" t="s">
         <v>75</v>
       </c>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2854,17 +3073,15 @@
     <hyperlink ref="C31" location="人员花名册!A1" display="截止目前人员花名册"/>
     <hyperlink ref="C30" location="研发设备清单!A1" display="研发设备一览表"/>
     <hyperlink ref="C32" location="人员月度情况统计表!A1" display="上年度月度情况统计表"/>
-    <hyperlink ref="C4" location="企业注册登记表!A1" display="企业注册登记表&#10;（新认定企业，包括国家级申报系统入库）"/>
+    <hyperlink ref="C4" location="企业注册登记表!A1" display="企业注册登记表_x000a_（新认定企业，包括国家级申报系统入库）"/>
   </hyperlinks>
   <pageMargins left="0.209027777777778" right="0.2" top="0.309027777777778" bottom="0.0777777777777778" header="0.179166666666667" footer="0.159027777777778"/>
-  <pageSetup paperSize="9" scale="70" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9" scale="70"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:I19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
@@ -2877,7 +3094,7 @@
     <col min="8" max="8" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="39" customHeight="1" spans="1:9">
+    <row r="1" spans="1:9" ht="39" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>76</v>
       </c>
@@ -2888,7 +3105,7 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" ht="18.75" spans="1:9">
+    <row r="2" spans="1:9" ht="18.75">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -2899,7 +3116,7 @@
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
     </row>
-    <row r="3" ht="28.5" spans="1:9">
+    <row r="3" spans="1:9" ht="28.5">
       <c r="A3" s="6" t="s">
         <v>77</v>
       </c>
@@ -2928,7 +3145,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" ht="21" customHeight="1" spans="1:9">
+    <row r="4" spans="1:9" ht="21" customHeight="1">
       <c r="A4" s="6">
         <v>1</v>
       </c>
@@ -2954,7 +3171,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" ht="21" customHeight="1" spans="1:9">
+    <row r="5" spans="1:9" ht="21" customHeight="1">
       <c r="A5" s="6">
         <v>2</v>
       </c>
@@ -2980,7 +3197,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" ht="21" customHeight="1" spans="1:9">
+    <row r="6" spans="1:9" ht="21" customHeight="1">
       <c r="A6" s="6">
         <v>3</v>
       </c>
@@ -3009,7 +3226,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" ht="21" customHeight="1" spans="1:9">
+    <row r="7" spans="1:9" ht="21" customHeight="1">
       <c r="A7" s="6">
         <v>4</v>
       </c>
@@ -3038,7 +3255,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" ht="21" customHeight="1" spans="1:9">
+    <row r="8" spans="1:9" ht="21" customHeight="1">
       <c r="A8" s="6">
         <v>5</v>
       </c>
@@ -3067,7 +3284,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" ht="21" customHeight="1" spans="1:9">
+    <row r="9" spans="1:9" ht="21" customHeight="1">
       <c r="A9" s="6">
         <v>6</v>
       </c>
@@ -3096,7 +3313,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" ht="21" customHeight="1" spans="1:9">
+    <row r="10" spans="1:9" ht="21" customHeight="1">
       <c r="A10" s="6">
         <v>7</v>
       </c>
@@ -3107,7 +3324,7 @@
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" ht="21" customHeight="1" spans="1:9">
+    <row r="11" spans="1:9" ht="21" customHeight="1">
       <c r="A11" s="6">
         <v>8</v>
       </c>
@@ -3118,7 +3335,7 @@
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
     </row>
-    <row r="12" ht="21" customHeight="1" spans="1:9">
+    <row r="12" spans="1:9" ht="21" customHeight="1">
       <c r="A12" s="6">
         <v>9</v>
       </c>
@@ -3129,7 +3346,7 @@
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
     </row>
-    <row r="13" ht="21" customHeight="1" spans="1:9">
+    <row r="13" spans="1:9" ht="21" customHeight="1">
       <c r="A13" s="6">
         <v>10</v>
       </c>
@@ -3140,7 +3357,7 @@
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
     </row>
-    <row r="14" ht="21" customHeight="1" spans="1:9">
+    <row r="14" spans="1:9" ht="21" customHeight="1">
       <c r="A14" s="6">
         <v>11</v>
       </c>
@@ -3151,7 +3368,7 @@
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" ht="21" customHeight="1" spans="1:9">
+    <row r="15" spans="1:9" ht="21" customHeight="1">
       <c r="A15" s="6">
         <v>12</v>
       </c>
@@ -3162,7 +3379,7 @@
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" ht="21" customHeight="1" spans="1:9">
+    <row r="16" spans="1:9" ht="21" customHeight="1">
       <c r="A16" s="6">
         <v>13</v>
       </c>
@@ -3173,7 +3390,7 @@
       <c r="F16" s="9"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" ht="21" customHeight="1" spans="1:7">
+    <row r="17" spans="1:9" ht="21" customHeight="1">
       <c r="A17" s="6">
         <v>14</v>
       </c>
@@ -3184,7 +3401,7 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" ht="21" customHeight="1" spans="1:7">
+    <row r="18" spans="1:9" ht="21" customHeight="1">
       <c r="A18" s="6">
         <v>15</v>
       </c>
@@ -3195,7 +3412,7 @@
       <c r="F18" s="9"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" ht="21" customHeight="1" spans="1:7">
+    <row r="19" spans="1:9" ht="21" customHeight="1">
       <c r="A19" s="6">
         <v>16</v>
       </c>
@@ -3226,7 +3443,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="1.45625" right="0.699305555555556" top="0.55" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
-  <headerFooter/>
+  <pageSetup orientation="landscape" paperSize="9"/>
 </worksheet>
 </file>
--- a/图云ITSS/资料整理/人员花名册.xlsx
+++ b/图云ITSS/资料整理/人员花名册.xlsx
@@ -1583,7 +1583,7 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="78">
+  <cellStyleXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
@@ -1617,6 +1617,11 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment/>
     </xf>
@@ -1831,7 +1836,7 @@
     <xf numFmtId="0" fontId="12" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="35" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="40" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1894,10 +1899,10 @@
     <xf numFmtId="0" fontId="12" fillId="34" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="35" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="40" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="9" xfId="35" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="9" xfId="40" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="36" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1916,7 +1921,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="64">
+  <cellStyles count="69">
     <cellStyle name="Normal" xfId="0"/>
     <cellStyle name="Percent" xfId="15"/>
     <cellStyle name="Currency" xfId="16"/>
@@ -1933,54 +1938,59 @@
     <cellStyle name="Currency [0]" xfId="27"/>
     <cellStyle name="Comma" xfId="28"/>
     <cellStyle name="Comma [0]" xfId="29"/>
-    <cellStyle name="千位分隔" xfId="30"/>
-    <cellStyle name="货币" xfId="31"/>
-    <cellStyle name="百分比" xfId="32"/>
-    <cellStyle name="千位分隔[0]" xfId="33"/>
-    <cellStyle name="货币[0]" xfId="34"/>
-    <cellStyle name="超链接" xfId="35"/>
-    <cellStyle name="已访问的超链接" xfId="36"/>
-    <cellStyle name="注释" xfId="37"/>
-    <cellStyle name="警告文本" xfId="38"/>
-    <cellStyle name="标题" xfId="39"/>
-    <cellStyle name="解释性文本" xfId="40"/>
-    <cellStyle name="标题 1" xfId="41"/>
-    <cellStyle name="标题 2" xfId="42"/>
-    <cellStyle name="标题 3" xfId="43"/>
-    <cellStyle name="标题 4" xfId="44"/>
-    <cellStyle name="输入" xfId="45"/>
-    <cellStyle name="输出" xfId="46"/>
-    <cellStyle name="计算" xfId="47"/>
-    <cellStyle name="检查单元格" xfId="48"/>
-    <cellStyle name="链接单元格" xfId="49"/>
-    <cellStyle name="汇总" xfId="50"/>
-    <cellStyle name="好" xfId="51"/>
-    <cellStyle name="差" xfId="52"/>
-    <cellStyle name="适中" xfId="53"/>
-    <cellStyle name="强调文字颜色 1" xfId="54"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="55"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="56"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="57"/>
-    <cellStyle name="强调文字颜色 2" xfId="58"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="59"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="60"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="61"/>
-    <cellStyle name="强调文字颜色 3" xfId="62"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="63"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="64"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="65"/>
-    <cellStyle name="强调文字颜色 4" xfId="66"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="67"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="68"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="69"/>
-    <cellStyle name="强调文字颜色 5" xfId="70"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="71"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="72"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="73"/>
-    <cellStyle name="强调文字颜色 6" xfId="74"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="75"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="76"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="77"/>
+    <cellStyle name="Percent" xfId="30"/>
+    <cellStyle name="Currency" xfId="31"/>
+    <cellStyle name="Currency [0]" xfId="32"/>
+    <cellStyle name="Comma" xfId="33"/>
+    <cellStyle name="Comma [0]" xfId="34"/>
+    <cellStyle name="千位分隔" xfId="35"/>
+    <cellStyle name="货币" xfId="36"/>
+    <cellStyle name="百分比" xfId="37"/>
+    <cellStyle name="千位分隔[0]" xfId="38"/>
+    <cellStyle name="货币[0]" xfId="39"/>
+    <cellStyle name="超链接" xfId="40"/>
+    <cellStyle name="已访问的超链接" xfId="41"/>
+    <cellStyle name="注释" xfId="42"/>
+    <cellStyle name="警告文本" xfId="43"/>
+    <cellStyle name="标题" xfId="44"/>
+    <cellStyle name="解释性文本" xfId="45"/>
+    <cellStyle name="标题 1" xfId="46"/>
+    <cellStyle name="标题 2" xfId="47"/>
+    <cellStyle name="标题 3" xfId="48"/>
+    <cellStyle name="标题 4" xfId="49"/>
+    <cellStyle name="输入" xfId="50"/>
+    <cellStyle name="输出" xfId="51"/>
+    <cellStyle name="计算" xfId="52"/>
+    <cellStyle name="检查单元格" xfId="53"/>
+    <cellStyle name="链接单元格" xfId="54"/>
+    <cellStyle name="汇总" xfId="55"/>
+    <cellStyle name="好" xfId="56"/>
+    <cellStyle name="差" xfId="57"/>
+    <cellStyle name="适中" xfId="58"/>
+    <cellStyle name="强调文字颜色 1" xfId="59"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="60"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="61"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="62"/>
+    <cellStyle name="强调文字颜色 2" xfId="63"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="64"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="65"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="66"/>
+    <cellStyle name="强调文字颜色 3" xfId="67"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="68"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="69"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="70"/>
+    <cellStyle name="强调文字颜色 4" xfId="71"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="72"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="73"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="74"/>
+    <cellStyle name="强调文字颜色 5" xfId="75"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="76"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="77"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="78"/>
+    <cellStyle name="强调文字颜色 6" xfId="79"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="80"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="81"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="82"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
